--- a/documentacion/matrices_de_prueba/PENSIONADOS_MATRIZ_DE_PRUEBAS.xlsx
+++ b/documentacion/matrices_de_prueba/PENSIONADOS_MATRIZ_DE_PRUEBAS.xlsx
@@ -5,17 +5,17 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\100102750\Desktop\Extraordinario_IngeSoft_2\Extraordinario_Software_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\100102750\Desktop\Extraordinario_IngeSoft_2\Extraordinario_Software_2\documentacion\matrices_de_prueba\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831EF666-E5FF-40D6-8D8F-1DC102726EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AB4E4B-3E30-4E24-B0AB-70F99700BE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{26B61DC6-C19F-4E8A-BB08-A22D00ACA84C}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz de pruebas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,23 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Nombre del Caso de Prueba</t>
-  </si>
-  <si>
-    <t>Motivo de la Prueba (Requerimiento/HU)</t>
-  </si>
-  <si>
     <t>Precondiciones</t>
   </si>
   <si>
-    <t>Pasos a Seguir</t>
-  </si>
-  <si>
     <t>Resultado Esperado</t>
   </si>
   <si>
@@ -89,17 +80,321 @@
     <t>Fecha de Ejecución</t>
   </si>
   <si>
-    <t>[DD/MM/AAAA]</t>
-  </si>
-  <si>
     <t>Cristian Ignacio Reyna Mendez</t>
+  </si>
+  <si>
+    <t>CP-05</t>
+  </si>
+  <si>
+    <t>CP-06</t>
+  </si>
+  <si>
+    <t>CP-07</t>
+  </si>
+  <si>
+    <t>CP-08</t>
+  </si>
+  <si>
+    <t>CP-09</t>
+  </si>
+  <si>
+    <t>CP-10</t>
+  </si>
+  <si>
+    <t>CP-11</t>
+  </si>
+  <si>
+    <t>CP-12</t>
+  </si>
+  <si>
+    <t>CP-13</t>
+  </si>
+  <si>
+    <t>CP-14</t>
+  </si>
+  <si>
+    <t>CP-15</t>
+  </si>
+  <si>
+    <t>[28/04/2026]</t>
+  </si>
+  <si>
+    <t>Título</t>
+  </si>
+  <si>
+    <t>Módulo / Categoría</t>
+  </si>
+  <si>
+    <t>Pasos de Prueba</t>
+  </si>
+  <si>
+    <t>Autenticación y control de acceso por rol</t>
+  </si>
+  <si>
+    <t>Seguridad / Login / Roles</t>
+  </si>
+  <si>
+    <t>Usuarios con roles Administrador, Operador y Pensionado registrados y activos. Pantalla de login disponible.</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión con credenciales válidas de cada rol (Admin, Operador, Pensionado) y verificar acceso al menú correcto.
+2. Intentar iniciar sesión con contraseña incorrecta y verificar rechazo con mensaje de error.
+3. Intentar acceder con usuario desactivado y verificar denegación de acceso.
+4. Con sesión de Operador, intentar acceder a módulos exclusivos del Administrador y verificar bloqueo con 'Acceso Denegado'.</t>
+  </si>
+  <si>
+    <t>Cada rol accede solo a sus funciones asignadas. Credenciales inválidas o usuarios desactivados no ingresan al sistema. Intentos de acceso no autorizado son bloqueados con mensaje claro.</t>
+  </si>
+  <si>
+    <t>Alta de usuario interno con validaciones de campos</t>
+  </si>
+  <si>
+    <t>Gestión de Usuarios Internos</t>
+  </si>
+  <si>
+    <t>Sesión iniciada como Administrador.</t>
+  </si>
+  <si>
+    <t>1. Acceder a 'Nuevo usuario', capturar nombre, correo, contraseña y rol 'Operador', guardar.
+2. Repetir el alta dejando el campo 'correo' vacío e intentar guardar.
+3. Verificar que el usuario creado en el paso 1 aparece en el listado con estado activo.</t>
+  </si>
+  <si>
+    <t>El alta exitosa crea el usuario con estado activo y aparece en el listado. El intento con campo obligatorio vacío muestra mensaje de validación y no guarda el registro.</t>
+  </si>
+  <si>
+    <t>Modificación, desactivación y asignación de roles a usuario interno</t>
+  </si>
+  <si>
+    <t>Sesión como Administrador. Usuario interno existente con rol Operador.</t>
+  </si>
+  <si>
+    <t>1. Seleccionar usuario interno, modificar nombre, guardar y verificar que el cambio se refleja en el expediente.
+2. Seleccionar usuario activo, ejecutar 'Desactivar', confirmar y verificar que no puede iniciar sesión.
+3. Editar usuario y cambiar rol a 'Administrador', guardar y verificar que obtiene acceso a módulos restringidos.
+4. Desde sesión Operador, intentar crear usuario interno y verificar que el acceso es denegado.</t>
+  </si>
+  <si>
+    <t>Cambios se reflejan correctamente. Usuarios desactivados no acceden al sistema. Rol Administrador concede permisos adicionales. Operador no puede crear usuarios internos.</t>
+  </si>
+  <si>
+    <t>Configuración de periodicidad y días de anticipación</t>
+  </si>
+  <si>
+    <t>Configuración del Proceso</t>
+  </si>
+  <si>
+    <t>Sesión como Administrador.</t>
+  </si>
+  <si>
+    <t>1. Acceder a configuración, ingresar '90' en periodicidad, guardar y verificar bitácora.
+2. Cambiar periodicidad de 90 a 30 días, guardar y verificar que el historial conserva el valor anterior.
+3. Ingresar '15' como días de anticipación para notificaciones, guardar.
+4. Con sesión Operador, intentar modificar periodicidad y verificar denegación de acceso.</t>
+  </si>
+  <si>
+    <t>Periodicidad y anticipación quedan configuradas correctamente. Historial conserva valores anteriores con registro de cambios. Operador no puede modificar estas configuraciones.</t>
+  </si>
+  <si>
+    <t>Alta de pensionado – flujo completo y validaciones obligatorias</t>
+  </si>
+  <si>
+    <t>Registro de Pensionados</t>
+  </si>
+  <si>
+    <t>Sesión como Administrador u Operador. Periodicidad configurada en 90 días.</t>
+  </si>
+  <si>
+    <t>1. Registrar pensionado con nombre, CURP y número de pensión, adjuntar credencial JPG, guardar.
+2. Verificar que la primera fecha de validación se calcula automáticamente (fecha alta + 90 días).
+3. Repetir el alta sin adjuntar credencial e intentar guardar.
+4. Intentar adjuntar archivo .docx como credencial.</t>
+  </si>
+  <si>
+    <t>Alta exitosa crea el expediente con primera fecha calculada automáticamente. Sin credencial, el sistema impide el guardado. Formatos no permitidos son rechazados con mensaje indicando tipos aceptados.</t>
+  </si>
+  <si>
+    <t>Prevención de duplicados – CURP y número de pensión</t>
+  </si>
+  <si>
+    <t>Registro de Pensionados / Integridad de Datos</t>
+  </si>
+  <si>
+    <t>Pensionado con CURP 'ABCD123456HDFXXX00' y número de pensión '00001' ya registrado.</t>
+  </si>
+  <si>
+    <t>1. Intentar registrar nuevo pensionado con la misma CURP y guardar.
+2. Intentar registrar nuevo pensionado con el mismo número de pensión '00001' y guardar.</t>
+  </si>
+  <si>
+    <t>Ambos intentos son rechazados con mensajes específicos indicando CURP o número de pensión duplicado. El registro no se guarda en ninguno de los casos.</t>
+  </si>
+  <si>
+    <t>Consulta y actualización del expediente del pensionado</t>
+  </si>
+  <si>
+    <t>Gestión de Expedientes</t>
+  </si>
+  <si>
+    <t>Sesión como Admin u Operador. Pensionado registrado con validaciones previas.</t>
+  </si>
+  <si>
+    <t>1. Buscar pensionado por nombre o CURP, seleccionar y abrir expediente completo.
+2. Verificar que muestra datos personales, credencial e historial de validaciones.
+3. Modificar teléfono y/o correo del pensionado, guardar y verificar que la acción queda en bitácora.
+4. Verificar que la credencial puede descargarse desde la sección de documentos adjuntos.</t>
+  </si>
+  <si>
+    <t>Expediente muestra información completa. Datos de contacto actualizados quedan en bitácora. Credencial disponible para descarga desde el expediente.</t>
+  </si>
+  <si>
+    <t>Estados de validación – Vigente, Próxima a vencer y Vencida</t>
+  </si>
+  <si>
+    <t>Control de Validaciones / Seguimiento</t>
+  </si>
+  <si>
+    <t>Pensionados con distintos estados de validación: uno con validación que vence en 10 días (anticipación = 15 días), otro que superó fecha límite y tolerancia.</t>
+  </si>
+  <si>
+    <t>1. Revisar listado de pensionados y verificar que se muestran columnas: última fecha, próxima fecha y estado.
+2. Verificar que el pensionado con vencimiento en 10 días aparece como 'Próxima a vencer'.
+3. Verificar que el pensionado que superó fecha límite y tolerancia aparece como 'Vencida' y en lista de alertas.
+4. Verificar que pensionado con validación reciente aparece como 'Vigente'.</t>
+  </si>
+  <si>
+    <t>Los tres estados se asignan correctamente según las fechas y la configuración. El listado refleja el estado actualizado de cada pensionado.</t>
+  </si>
+  <si>
+    <t>Portal del pensionado – visualización de aviso y formulario de validación</t>
+  </si>
+  <si>
+    <t>Portal Pensionado</t>
+  </si>
+  <si>
+    <t>Sesión como Pensionado. Validación en estado 'Próxima a vencer'.</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión y revisar pantalla principal; verificar que se muestra aviso con fecha límite.
+2. Acceder al formulario de validación de supervivencia.
+3. Marcar confirmación expresa, agregar observaciones opcionales, adjuntar foto JPG y enviar.
+4. Verificar que la próxima fecha de validación se recalcula automáticamente.</t>
+  </si>
+  <si>
+    <t>Aviso de validación pendiente visible en la pantalla principal. Formulario completado queda registrado con fecha, hora, confirmación, evidencia y observaciones. Próxima fecha actualizada automáticamente.</t>
+  </si>
+  <si>
+    <t>Historial y trazabilidad de validaciones del pensionado</t>
+  </si>
+  <si>
+    <t>Historial de Validaciones</t>
+  </si>
+  <si>
+    <t>Pensionado con al menos 3 validaciones registradas, incluyendo una marcada como 'Rechazada'.</t>
+  </si>
+  <si>
+    <t>1. Abrir expediente y acceder a 'Historial de validaciones'.
+2. Verificar listado cronológico con fecha, hora, resultado y evidencias.
+3. Localizar la validación rechazada y confirmar que está visible y no puede eliminarse.</t>
+  </si>
+  <si>
+    <t>Historial muestra todas las validaciones en orden cronológico. La validación rechazada permanece visible e inamovible en el historial.</t>
+  </si>
+  <si>
+    <t>Restricciones del pensionado – validación fuera de período y acceso a expedientes ajenos</t>
+  </si>
+  <si>
+    <t>Seguridad / Control de Acceso Pensionado</t>
+  </si>
+  <si>
+    <t>Sesión como Pensionado con validación en estado 'Vigente'.</t>
+  </si>
+  <si>
+    <t>1. Intentar acceder al formulario de validación cuando no hay validación pendiente.
+2. Verificar que la pantalla principal solo muestra la próxima fecha programada.
+3. Intentar acceder a la URL del expediente de otro pensionado.</t>
+  </si>
+  <si>
+    <t>El sistema impide realizar validación fuera de período, indicando que no hay validación pendiente. Intentar acceder a expediente ajeno resulta en 'Acceso Denegado'.</t>
+  </si>
+  <si>
+    <t>Período de tolerancia y estado crítico por incumplimiento</t>
+  </si>
+  <si>
+    <t>Control de Validaciones / Alertas</t>
+  </si>
+  <si>
+    <t>Pensionado cuya validación venció hace 2 días; período de tolerancia configurado en 5 días.</t>
+  </si>
+  <si>
+    <t>1. Revisar el estado del pensionado en el listado general.
+2. Verificar que el estado es 'Vencida' pero que aún no se clasifica como caso crítico.
+3. Avanzar la fecha simulada a 6 días después del vencimiento y verificar que pasa a caso crítico.</t>
+  </si>
+  <si>
+    <t>El sistema aplica correctamente el período de tolerancia. El expediente pasa a caso crítico solo al superar la tolerancia configurada.</t>
+  </si>
+  <si>
+    <t>Filtrado y seguimiento del padrón por estado y criterios de búsqueda</t>
+  </si>
+  <si>
+    <t>Módulo de Seguimiento / Búsquedas</t>
+  </si>
+  <si>
+    <t>Sesión como Operador. Padrón con pensionados en distintos estados.</t>
+  </si>
+  <si>
+    <t>1. Filtrar por estado 'Próxima a vencer' y verificar resultados ordenados por fecha de vencimiento.
+2. Filtrar por estado 'Vencida' y verificar listado con datos de contacto.
+3. Filtrar por estado 'En Revisión' y verificar que solo se muestran esos registros.
+4. Buscar por nombre parcial y verificar coincidencias.
+5. Buscar por CURP parcial y verificar resultados.</t>
+  </si>
+  <si>
+    <t>Cada filtro devuelve únicamente los registros correspondientes. Búsquedas por nombre y CURP muestran coincidencias correctas.</t>
+  </si>
+  <si>
+    <t>Dashboard, reportes y bitácora del sistema</t>
+  </si>
+  <si>
+    <t>Reportes / Dashboard / Auditoría</t>
+  </si>
+  <si>
+    <t>Sesión con permisos activos. Alta de pensionado completada. Cambio de periodicidad registrado.</t>
+  </si>
+  <si>
+    <t>1. Acceder al dashboard y verificar indicadores: total de pensionados, vigentes, vencidos y en revisión.
+2. Generar reporte 'Próximas a vencer' y verificar que incluye pensionados con fecha correspondiente.
+3. Consultar bitácora y verificar registro del alta del pensionado con: usuario, acción, fecha y hora.
+4. Consultar historial de cambios en configuración y verificar que muestra valor anterior, nuevo valor, usuario y fecha.</t>
+  </si>
+  <si>
+    <t>Dashboard refleja indicadores actualizados. Reporte generado correctamente. Bitácora registra todas las acciones con datos completos. Historial de configuración conserva el rastro de cambios.</t>
+  </si>
+  <si>
+    <t>Seguridad de datos, rendimiento y usabilidad general</t>
+  </si>
+  <si>
+    <t>Seguridad / NFR / Usabilidad</t>
+  </si>
+  <si>
+    <t>Sistema en operación. Usuario nuevo creado. Al menos 500 registros de pensionados en BD.</t>
+  </si>
+  <si>
+    <t>1. Crear usuario y consultar tabla en BD; verificar que la contraseña está cifrada.
+2. Intentar eliminar un expediente de pensionado y verificar que solo existe la opción de desactivar.
+3. Realizar búsqueda de pensionados por nombre y medir tiempo de respuesta.
+4. Navegar por los módulos principales y provocar al menos dos mensajes de validación; revisar redacción.</t>
+  </si>
+  <si>
+    <t>Contraseñas almacenadas como hash, no en texto plano. Expedientes no pueden eliminarse físicamente. Búsquedas responden en menos de 3 segundos. Todos los mensajes están en español claro y sin tecnicismos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +415,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -129,7 +430,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -152,48 +453,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -201,47 +465,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -252,6 +493,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FDC2EF4D-5719-42B0-8AE6-90940A6503C6}" name="Tabla1" displayName="Tabla1" ref="B8:G23" totalsRowShown="0">
+  <autoFilter ref="B8:G23" xr:uid="{FDC2EF4D-5719-42B0-8AE6-90940A6503C6}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{408CE6E0-2E54-4EDA-BDE5-12DFFCB84A0C}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{AA48DC6A-6153-4988-9611-559311E544BA}" name="Título"/>
+    <tableColumn id="3" xr3:uid="{D61FAFC6-EFF8-42D9-A081-C69224DCDA31}" name="Módulo / Categoría"/>
+    <tableColumn id="4" xr3:uid="{F8F0D4A9-8DCE-46AA-9E92-410EA79A9D80}" name="Precondiciones"/>
+    <tableColumn id="5" xr3:uid="{AA309012-F617-40E2-9884-B988359311BA}" name="Pasos de Prueba" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{3E659512-F363-4470-BB28-3694C15241FF}" name="Resultado Esperado" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,242 +828,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75A8BB2-AD50-49F1-A57A-8CA0A6E88689}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="B1:G26"/>
+  <dimension ref="B1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="142" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="79.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="103.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="10"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="10"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="13"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="10"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="10"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="10"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="11"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="10"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="10"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="10"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="10"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="10"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="11"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="10"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="11"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-    </row>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B16:B22"/>
-    <mergeCell ref="C16:C22"/>
-    <mergeCell ref="D16:D22"/>
-    <mergeCell ref="E16:E22"/>
-    <mergeCell ref="G16:G22"/>
-    <mergeCell ref="B9:B15"/>
-    <mergeCell ref="C9:C15"/>
-    <mergeCell ref="D9:D15"/>
-    <mergeCell ref="E9:E15"/>
-    <mergeCell ref="G9:G15"/>
-  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>